--- a/RESULTS/2025/CLASS/SS1/English_language/results.xlsx
+++ b/RESULTS/2025/CLASS/SS1/English_language/results.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,52 +465,6 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>Submitted At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Korede Samuel</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>std178</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ENGLISH</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2025-12-13 19:32</t>
         </is>
       </c>
     </row>

--- a/RESULTS/2025/CLASS/SS1/English_language/results.xlsx
+++ b/RESULTS/2025/CLASS/SS1/English_language/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,42 +429,52 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Class Level</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Class Arm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Score (%)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Time Taken</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Submitted At</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Term</t>
         </is>
       </c>
     </row>
